--- a/youtube-links.xlsx
+++ b/youtube-links.xlsx
@@ -11,15 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Execution Time (Calgary)</t>
   </si>
   <si>
     <t>YouTube URL</t>
-  </si>
-  <si>
-    <t>2026-10-15 14:44:04</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=GKLiB4WTkRc</t>
@@ -410,17 +407,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
